--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486682_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486682_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5675</v>
+        <v>11.0048</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5533</v>
+        <v>8.766999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0143</v>
+        <v>2.2378</v>
       </c>
       <c r="G2" t="n">
         <v>8.7524</v>
@@ -610,13 +610,13 @@
         <v>0.7723</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4523</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3031</v>
+        <v>0.5169</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1492</v>
+        <v>0.3727</v>
       </c>
       <c r="V2" t="n">
         <v>1.5559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5291</v>
+        <v>1.5775</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6051</v>
+        <v>0.7778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.7998</v>
       </c>
       <c r="G3" t="n">
         <v>0.2122</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9307</v>
+        <v>0.9792</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4617</v>
+        <v>0.6343</v>
       </c>
       <c r="U3" t="n">
-        <v>0.469</v>
+        <v>0.3449</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5558</v>
+        <v>0.5928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0289</v>
+        <v>0.7115</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5269</v>
+        <v>-0.1187</v>
       </c>
       <c r="G4" t="n">
         <v>0.5583</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6459</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0485</v>
+        <v>-0.3658</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6944</v>
+        <v>1.0488</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3381</v>
+        <v>0.4317</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5452</v>
+        <v>0.2317</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8833</v>
+        <v>0.2001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6073</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.6419</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1311</v>
+        <v>0.1469</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1529</v>
+        <v>3.1625</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8424</v>
+        <v>2.9184</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6895</v>
+        <v>0.2442</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5456</v>
+        <v>-2.3738</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1039</v>
+        <v>-2.2765</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5583</v>
+        <v>-0.0973</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7377</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8547</v>
+        <v>0.5311</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2407</v>
+        <v>-0.0347</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.386</v>
+        <v>0.5658</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6138</v>
+        <v>0.6565</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0.6565</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0063</v>
+        <v>0.3537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4094</v>
+        <v>0.7197</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4157</v>
+        <v>-0.366</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2325</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.353</v>
+        <v>0.0069</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2484</v>
+        <v>0.0619</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1047</v>
+        <v>-0.055</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3641</v>
+        <v>-0.3374</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3406</v>
+        <v>-1.469</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0234</v>
+        <v>1.1316</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.6073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6419</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1469</v>
+        <v>-0.1311</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1625</v>
+        <v>1.1529</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9184</v>
+        <v>1.8424</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2442</v>
+        <v>-0.6895</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3738</v>
+        <v>-0.5456</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2765</v>
+        <v>-1.1039</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0973</v>
+        <v>0.5583</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5446</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2647</v>
+        <v>0.1791</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>0.3169</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3423</v>
+        <v>-0.1377</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6565</v>
+        <v>0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X7" t="n">
         <v>0.6565</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8167</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0344</v>
+        <v>0.1912</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2177</v>
+        <v>-1.1806</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8206</v>
+        <v>-2.8721</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7174</v>
+        <v>-3.496</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1032</v>
+        <v>0.6239</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3376</v>
+        <v>0.3224</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0414</v>
+        <v>-0.9436</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.379</v>
+        <v>1.266</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.483</v>
+        <v>-3.1945</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7588</v>
+        <v>-2.5524</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2758</v>
+        <v>-0.6421</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4247</v>
+        <v>0.8827</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3032</v>
+        <v>0.2204</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1215</v>
+        <v>0.6624</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9949</v>
+        <v>-1.0966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.136</v>
+        <v>-1.2895</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1309</v>
+        <v>0.1928</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8721</v>
+        <v>-1.8206</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.496</v>
+        <v>-0.7174</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6239</v>
+        <v>-1.1032</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3224</v>
+        <v>-1.3376</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9436</v>
+        <v>0.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>1.266</v>
+        <v>-1.379</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1945</v>
+        <v>-0.483</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5524</v>
+        <v>-0.7588</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6421</v>
+        <v>0.2758</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8772</v>
+        <v>0.1447</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1652</v>
+        <v>0.0481</v>
       </c>
       <c r="U9" t="n">
-        <v>0.712</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8103</v>
+        <v>-1.3703</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7975</v>
+        <v>-1.432</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0128</v>
+        <v>0.0617</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3598</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.033</v>
+        <v>0.4069</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0551</v>
+        <v>0.4205</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0881</v>
+        <v>-0.0136</v>
       </c>
       <c r="V10" t="n">
         <v>1.5133</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5183</v>
+        <v>-2.6851</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3327</v>
+        <v>-3.3258</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8145</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9666</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.491</v>
+        <v>0.3241</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1927</v>
+        <v>0.1997</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2983</v>
+        <v>0.1245</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6565</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1165</v>
+        <v>-5.2904</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8818</v>
+        <v>-3.2543</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2347</v>
+        <v>-2.036</v>
       </c>
       <c r="G13" t="n">
         <v>-2.142</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7501</v>
+        <v>0.076</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8002</v>
+        <v>-0.1727</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0501</v>
+        <v>0.2487</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3282</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1006</v>
+        <v>-1.2727</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.345499999999999</v>
+        <v>-1.517700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2450999999999994</v>
+        <v>0.2450999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6910000000000009</v>
+        <v>-0.6910000000000018</v>
       </c>
       <c r="H14" t="n">
         <v>-12.4122</v>
@@ -1546,13 +1546,13 @@
         <v>9.6538</v>
       </c>
       <c r="S14" t="n">
-        <v>4.275799999999999</v>
+        <v>5.1034</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6864999999999999</v>
+        <v>1.5144</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5892</v>
+        <v>3.5893</v>
       </c>
       <c r="V14" t="n">
         <v>3.9686</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7023</v>
+        <v>4.1008</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5838</v>
+        <v>2.894</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1186</v>
+        <v>1.2068</v>
       </c>
       <c r="G15" t="n">
         <v>1.3342</v>
@@ -1624,13 +1624,13 @@
         <v>3.2823</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0537</v>
+        <v>-0.6552</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0486</v>
+        <v>-0.7383</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0051</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.1049</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.508</v>
+        <v>3.912</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4308</v>
+        <v>1.5342</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0772</v>
+        <v>2.3778</v>
       </c>
       <c r="G16" t="n">
         <v>1.8614</v>
@@ -1702,13 +1702,13 @@
         <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7833</v>
+        <v>-0.3792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2211</v>
+        <v>-0.1177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5622</v>
+        <v>-0.2616</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0801</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5628</v>
+        <v>2.1009</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3774</v>
+        <v>1.6534</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1854</v>
+        <v>0.4474</v>
       </c>
       <c r="G17" t="n">
         <v>1.9025</v>
@@ -1780,13 +1780,13 @@
         <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>0.386</v>
+        <v>-0.0759</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6616</v>
+        <v>-0.0624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2756</v>
+        <v>-0.0136</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2703</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5292</v>
+        <v>0.4176</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0005</v>
+        <v>0.6902</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4713</v>
+        <v>-0.2727</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7998</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2976</v>
+        <v>0.186</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1652</v>
+        <v>-0.1451</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1324</v>
+        <v>0.3311</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8995</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4808</v>
+        <v>-0.1857</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1261</v>
+        <v>1.333</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6069</v>
+        <v>-1.5187</v>
       </c>
       <c r="G19" t="n">
         <v>1.5383</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0537</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1865</v>
+        <v>-0.9796</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1328</v>
+        <v>0.221</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0096</v>
+        <v>-0.4621</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5028</v>
+        <v>-0.1925</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5068</v>
+        <v>-0.2696</v>
       </c>
       <c r="G20" t="n">
         <v>0.6965</v>
@@ -2014,13 +2014,13 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.1586</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4966</v>
+        <v>-0.1864</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2095</v>
+        <v>0.0278</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5744</v>
+        <v>-1.5732</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5803</v>
+        <v>-2.27</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0059</v>
+        <v>0.6968</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9593</v>
@@ -2092,13 +2092,13 @@
         <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1874</v>
+        <v>-0.1862</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8279</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6405</v>
+        <v>0.3314</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7792</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.254</v>
+        <v>-1.8003</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9255</v>
+        <v>-2.8221</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6715</v>
+        <v>1.0218</v>
       </c>
       <c r="G22" t="n">
         <v>-1.582</v>
@@ -2170,13 +2170,13 @@
         <v>2.8962</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9434</v>
+        <v>-0.4897</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5522</v>
+        <v>-0.4488</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3912</v>
+        <v>-0.0409</v>
       </c>
       <c r="V22" t="n">
         <v>-0.694</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.883</v>
+        <v>-3.0305</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7549</v>
+        <v>-3.0652</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1281</v>
+        <v>0.0347</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3007</v>
@@ -2248,13 +2248,13 @@
         <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2318</v>
+        <v>-0.3794</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0832</v>
+        <v>-0.3935</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1486</v>
+        <v>0.0141</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7366</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.1005</v>
+        <v>3.479499999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2448999999999995</v>
+        <v>-0.2449999999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3455</v>
+        <v>3.7243</v>
       </c>
       <c r="G24" t="n">
         <v>0.6910999999999992</v>
@@ -2326,13 +2326,13 @@
         <v>19.3077</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.2758</v>
+        <v>-2.8968</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5893</v>
+        <v>-3.589399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6865000000000001</v>
+        <v>0.6924</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9686</v>
